--- a/uploadfile/student_list_upload.xlsx
+++ b/uploadfile/student_list_upload.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erice\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0-Python\2026ipuregreen\uploadfile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{300C37BA-C7C0-4251-AA87-9D609DD16C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B38891-75E2-46B0-9EFC-718C5A61ED86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="學員清單" sheetId="2" r:id="rId1"/>
+    <sheet name="學員名單" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
